--- a/artfynd/A 12093-2023 artfynd.xlsx
+++ b/artfynd/A 12093-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12093-2023 artfynd.xlsx
+++ b/artfynd/A 12093-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,63 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108117</v>
+        <v>7019515</v>
       </c>
       <c r="B2" t="n">
-        <v>77486</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>336</v>
+        <v>1435</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flatenberget, Dlr</t>
+          <t>Flatenberget. Stångmyrberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506280.9169549107</v>
+        <v>506159</v>
       </c>
       <c r="R2" t="n">
-        <v>6686456.872788716</v>
+        <v>6686260</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +755,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-04-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-04-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tidigare funnen här bl.a. 17 aug 1997</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,169 +774,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gammal en i örtrik granskog</t>
+          <t>Skogsbete t o m 1940-talet</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Anders Janols</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>7019515</v>
-      </c>
-      <c r="B3" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1435</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bitter taggsvamp</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Hydnellum fennicum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Flatenberget. Stångmyrberg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>506159.1612104646</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6686259.955636918</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2013-08-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2013-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tidigare funnen här bl.a. 17 aug 1997</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Ängsblandskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsbete t o m 1940-talet</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Anders Janols</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Anders Janols</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
